--- a/docs/dossiers/dossier-paris-1er-arrondissement-e3ade82a.xlsx
+++ b/docs/dossiers/dossier-paris-1er-arrondissement-e3ade82a.xlsx
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>3 000 à 6 500 €/m²</t>
+          <t>6 954 à 15 574 €/m²</t>
         </is>
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>ce bien est 46 % SOUS la médiane locale</t>
+          <t>ce bien est 78 % SOUS la médiane locale</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,12 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>référentiel interne</t>
+          <t>198 ventes réelles 2023-2025 (DVF)</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>DVF = prix réellement payés, enregistrés chez le notaire (data.gouv.fr)</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2290,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>référentiel interne</t>
+          <t>198 ventes réelles 2023-2025 (DVF)</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-1er-arrondissement-e3ade82a.xlsx
+++ b/docs/dossiers/dossier-paris-1er-arrondissement-e3ade82a.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
